--- a/static/files/logements.xlsx
+++ b/static/files/logements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3FCFED-12B3-4140-8933-88B3408D72CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CD73E-B016-E748-92F2-005EE1D5224B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34480" yWindow="4440" windowWidth="27020" windowHeight="16440" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
+    <workbookView xWindow="1000" yWindow="500" windowWidth="27800" windowHeight="17500" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Logements" sheetId="1" r:id="rId1"/>
@@ -117,23 +117,23 @@
 (article R.111-2)</t>
   </si>
   <si>
-    <t>Loyer maxinum en € par m² de surface utile</t>
-  </si>
-  <si>
-    <t>Loyer maxinum du logement en €
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
+  </si>
+  <si>
+    <t>elle sera calculée automatiquement lors de l'import des logements</t>
+  </si>
+  <si>
+    <t>Loyer maximum en € par m² de surface utile</t>
+  </si>
+  <si>
+    <t>Loyer maximum du logement en €
 (col 4 * col 5 * col 6)</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
-  </si>
-  <si>
-    <t>elle sera calculée automatiquement lors de l'import des logements</t>
   </si>
 </sst>
 </file>
@@ -362,13 +362,13 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,27 +788,27 @@
         <v>21</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
       <c r="C2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="33"/>
+      <c r="E2" s="34"/>
       <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
@@ -821,8 +821,8 @@
       <c r="I2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="34" t="s">
-        <v>29</v>
+      <c r="J2" s="32" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -836,7 +836,7 @@
       <c r="H3" s="29"/>
       <c r="I3" s="24"/>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1426,7 +1426,7 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">

--- a/static/files/logements.xlsx
+++ b/static/files/logements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CD73E-B016-E748-92F2-005EE1D5224B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C135054F-4AF9-8143-9EC4-056FAEEA0AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="500" windowWidth="27800" windowHeight="17500" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>

--- a/static/files/logements.xlsx
+++ b/static/files/logements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766A3302-9577-CC42-AD97-210C347D5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{766A3302-9577-CC42-AD97-210C347D5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C9AAF17-0C0A-4CE4-BB04-6E50FA35993D}"/>
   <bookViews>
     <workbookView xWindow="33440" yWindow="1860" windowWidth="28880" windowHeight="16440" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Notice" sheetId="2" r:id="rId2"/>
     <sheet name="Data" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,93 +38,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>Ici quelques explications</t>
-  </si>
-  <si>
-    <t>1. Telechager le modèle (ce fichier)</t>
-  </si>
-  <si>
-    <t>3. Enregistrer vos modifications</t>
-  </si>
-  <si>
-    <t>4. Téléverser le fichier modifié dans l'application</t>
-  </si>
-  <si>
-    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t>Désignation des logements</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Coefficient propre au logement</t>
-  </si>
-  <si>
-    <t>Type de logement</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>Col 1</t>
-  </si>
-  <si>
-    <t>Col 2</t>
-  </si>
-  <si>
-    <t>Col 3</t>
-  </si>
-  <si>
-    <t>Col 4</t>
-  </si>
-  <si>
-    <t>Col 5</t>
-  </si>
-  <si>
-    <t>Col 6</t>
-  </si>
-  <si>
-    <t>Col 7</t>
-  </si>
-  <si>
-    <t>Désignation des logements</t>
+    <t>Financement</t>
+  </si>
+  <si>
+    <t>Surface habitable
+(article R.156-1)</t>
+  </si>
+  <si>
+    <t>Surface des annexes
+Réelle</t>
+  </si>
+  <si>
+    <t>Surface des annexes
+Retenue dans la SU</t>
   </si>
   <si>
     <t>Surface utile
 (surface habitable augmentée de 50% de la surface des annexes)</t>
   </si>
   <si>
-    <t>Surface des annexes
-Retenue dans la SU</t>
-  </si>
-  <si>
-    <t>Surface des annexes
-Réelle</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
-  </si>
-  <si>
-    <t>elle sera calculée automatiquement lors de l'import des logements</t>
-  </si>
-  <si>
     <t>Loyer maximum en € par m² de surface utile</t>
+  </si>
+  <si>
+    <t>Coefficient propre au logement</t>
   </si>
   <si>
     <t>Loyer maximum du logement en €
@@ -135,23 +81,85 @@
     <t>Par défaut, indiquez un coefficient de 1 si vous n’appliquez pas de pondération particulière)</t>
   </si>
   <si>
+    <t>Col 1</t>
+  </si>
+  <si>
+    <t>Col 2</t>
+  </si>
+  <si>
+    <t>Col 3</t>
+  </si>
+  <si>
+    <t>Col 4</t>
+  </si>
+  <si>
+    <t>Col 5</t>
+  </si>
+  <si>
+    <t>Col 6</t>
+  </si>
+  <si>
+    <t>Col 7</t>
+  </si>
+  <si>
+    <t>Col 8</t>
+  </si>
+  <si>
+    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
+  </si>
+  <si>
+    <t>elle sera calculée automatiquement lors de l'import des logements</t>
+  </si>
+  <si>
+    <t>Ici quelques explications</t>
+  </si>
+  <si>
+    <t>1. Telechager le modèle (ce fichier)</t>
+  </si>
+  <si>
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>3. Enregistrer vos modifications</t>
+  </si>
+  <si>
+    <t>4. Téléverser le fichier modifié dans l'application</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+  </si>
+  <si>
+    <t>Type de logement</t>
+  </si>
+  <si>
     <t>lignes data</t>
   </si>
   <si>
-    <t>Surface habitable
-(article R.156-1)</t>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T1bis</t>
+  </si>
+  <si>
+    <t>T1'</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
   </si>
   <si>
     <t>T5</t>
   </si>
   <si>
     <t>T6 et plus</t>
-  </si>
-  <si>
-    <t>T1'</t>
-  </si>
-  <si>
-    <t>T1bis</t>
   </si>
 </sst>
 </file>
@@ -162,7 +170,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-40C]"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -370,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -415,6 +423,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -461,6 +472,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -470,13 +488,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -520,7 +531,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}" name="type" displayName="type" ref="A1:A9" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}" name="type" displayName="type" ref="A1:A9" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="2" tableBorderDxfId="3" totalsRowBorderDxfId="1">
   <autoFilter ref="A1:A9" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{68B921AF-0801-1140-A800-5EFE7005DB88}" name="Type de logement" dataDxfId="0"/>
@@ -530,9 +541,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -570,7 +581,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -676,7 +687,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -818,7 +829,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -826,777 +837,830 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08021C90-1ACF-2A4C-A1B0-58A48A8F7007}">
-  <dimension ref="A1:Q52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P52"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
+    <col min="2" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
+    <col min="10" max="10" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="51.75" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="H1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="96.75">
       <c r="A2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="1:17" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:16" ht="18.75">
+      <c r="A3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="34" t="s">
         <v>15</v>
       </c>
+      <c r="F3" s="34"/>
       <c r="G3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.95" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="9"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="24" t="str">
-        <f>IF(F4*G4*H4&gt;0,F4*G4*H4,"")</f>
-        <v/>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" s="14"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="24" t="str">
+        <f>IF(G4*H4*I4&gt;0,G4*H4*I4,"")</f>
+        <v/>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.95" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="25" t="str">
-        <f>IF(F5*G5*H5&gt;0,F5*G5*H5,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" s="15"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25" t="str">
+        <f>IF(G5*H5*I5&gt;0,G5*H5*I5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.95" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="24" t="str">
-        <f t="shared" ref="I6:I52" si="0">IF(F6*G6*H6&gt;0,F6*G6*H6,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G6" s="14"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="24" t="str">
+        <f>IF(G6*H6*I6&gt;0,G6*H6*I6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.95" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="4"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="25" t="str">
+        <f>IF(G7*H7*I7&gt;0,G7*H7*I7,"")</f>
+        <v/>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:16" ht="15.95" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="4"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="24" t="str">
+        <f>IF(G8*H8*I8&gt;0,G8*H8*I8,"")</f>
+        <v/>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:16" ht="15.95" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" s="15"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="25" t="str">
+        <f>IF(G9*H9*I9&gt;0,G9*H9*I9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.95" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" s="14"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="24" t="str">
+        <f>IF(G10*H10*I10&gt;0,G10*H10*I10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.95" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" s="15"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="25" t="str">
+        <f>IF(G11*H11*I11&gt;0,G11*H11*I11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.95" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G12" s="14"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="24" t="str">
+        <f>IF(G12*H12*I12&gt;0,G12*H12*I12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.95" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G13" s="15"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="25" t="str">
+        <f>IF(G13*H13*I13&gt;0,G13*H13*I13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.95" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G14" s="14"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="24" t="str">
+        <f>IF(G14*H14*I14&gt;0,G14*H14*I14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.95" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G15" s="15"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="25" t="str">
+        <f>IF(G15*H15*I15&gt;0,G15*H15*I15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.95" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="14"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="24" t="str">
+        <f>IF(G16*H16*I16&gt;0,G16*H16*I16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.95" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G17" s="15"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="25" t="str">
+        <f>IF(G17*H17*I17&gt;0,G17*H17*I17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.95" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="14"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="24" t="str">
+        <f>IF(G18*H18*I18&gt;0,G18*H18*I18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.95" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="15"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="25" t="str">
+        <f>IF(G19*H19*I19&gt;0,G19*H19*I19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.95" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G20" s="14"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="24" t="str">
+        <f>IF(G20*H20*I20&gt;0,G20*H20*I20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.95" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G21" s="15"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="25" t="str">
+        <f>IF(G21*H21*I21&gt;0,G21*H21*I21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.95" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" s="14"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="24" t="str">
+        <f>IF(G22*H22*I22&gt;0,G22*H22*I22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.95" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="15"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="25" t="str">
+        <f>IF(G23*H23*I23&gt;0,G23*H23*I23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.95" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" s="14"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="24" t="str">
+        <f>IF(G24*H24*I24&gt;0,G24*H24*I24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.95" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" s="15"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="25" t="str">
+        <f>IF(G25*H25*I25&gt;0,G25*H25*I25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.95" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="14"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="24" t="str">
+        <f>IF(G26*H26*I26&gt;0,G26*H26*I26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.95" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="15"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="25" t="str">
+        <f>IF(G27*H27*I27&gt;0,G27*H27*I27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.95" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="14"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="24" t="str">
+        <f>IF(G28*H28*I28&gt;0,G28*H28*I28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.95" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="15"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="25" t="str">
+        <f>IF(G29*H29*I29&gt;0,G29*H29*I29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.95" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="14"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="24" t="str">
+        <f>IF(G30*H30*I30&gt;0,G30*H30*I30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.95" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="15"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="25" t="str">
+        <f>IF(G31*H31*I31&gt;0,G31*H31*I31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.95" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="14"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="24" t="str">
+        <f>IF(G32*H32*I32&gt;0,G32*H32*I32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.95" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="15"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="25" t="str">
+        <f>IF(G33*H33*I33&gt;0,G33*H33*I33,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.95" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="14"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="24" t="str">
+        <f>IF(G34*H34*I34&gt;0,G34*H34*I34,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.95" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="15"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="25" t="str">
+        <f>IF(G35*H35*I35&gt;0,G35*H35*I35,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.95" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="14"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="24" t="str">
+        <f>IF(G36*H36*I36&gt;0,G36*H36*I36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.95" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="15"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="25" t="str">
+        <f>IF(G37*H37*I37&gt;0,G37*H37*I37,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.95" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="14"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="24" t="str">
+        <f>IF(G38*H38*I38&gt;0,G38*H38*I38,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.95" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="15"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="25" t="str">
+        <f>IF(G39*H39*I39&gt;0,G39*H39*I39,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.95" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="14"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="24" t="str">
+        <f>IF(G40*H40*I40&gt;0,G40*H40*I40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.95" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="15"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="25" t="str">
+        <f>IF(G41*H41*I41&gt;0,G41*H41*I41,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.95" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="14"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="24" t="str">
+        <f>IF(G42*H42*I42&gt;0,G42*H42*I42,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.95" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="7"/>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" s="15"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="25" t="str">
+        <f>IF(G43*H43*I43&gt;0,G43*H43*I43,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.95" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" s="14"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="24" t="str">
+        <f>IF(G44*H44*I44&gt;0,G44*H44*I44,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.95" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="7"/>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" s="15"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="25" t="str">
+        <f>IF(G45*H45*I45&gt;0,G45*H45*I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.95" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G46" s="14"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="24" t="str">
+        <f>IF(G46*H46*I46&gt;0,G46*H46*I46,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.95" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="7"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G47" s="15"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="25" t="str">
+        <f>IF(G47*H47*I47&gt;0,G47*H47*I47,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.95" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G48" s="14"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="24" t="str">
+        <f>IF(G48*H48*I48&gt;0,G48*H48*I48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.95" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="7"/>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G49" s="15"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="25" t="str">
+        <f>IF(G49*H49*I49&gt;0,G49*H49*I49,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.95" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G50" s="14"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="24" t="str">
+        <f>IF(G50*H50*I50&gt;0,G50*H50*I50,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.95" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="7"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" s="15"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="25" t="str">
+        <f>IF(G51*H51*I51&gt;0,G51*H51*I51,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.95" customHeight="1">
       <c r="A52" s="5"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -1606,21 +1670,21 @@
       <c r="G52" s="19"/>
       <c r="H52" s="23"/>
       <c r="I52" s="26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I52" si="0">IF(F52*G52*H52&gt;0,F52*G52*H52,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1643,45 +1707,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467F41B6-50A5-F34D-9811-537B9541F979}">
   <dimension ref="B2:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1693,62 +1757,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4880C39C-0BD9-B447-909B-7F37D33CA805}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E1" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="30">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="31"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/static/files/logements.xlsx
+++ b/static/files/logements.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayoub.bouchachia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766A3302-9577-CC42-AD97-210C347D5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9CB336-2071-427E-BEF6-2274AED39178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33440" yWindow="1860" windowWidth="28880" windowHeight="16440" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
+    <workbookView xWindow="-16110" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Logements" sheetId="1" r:id="rId1"/>
     <sheet name="Notice" sheetId="2" r:id="rId2"/>
     <sheet name="Data" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,93 +38,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>Ici quelques explications</t>
-  </si>
-  <si>
-    <t>1. Telechager le modèle (ce fichier)</t>
-  </si>
-  <si>
-    <t>3. Enregistrer vos modifications</t>
-  </si>
-  <si>
-    <t>4. Téléverser le fichier modifié dans l'application</t>
-  </si>
-  <si>
-    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t>Désignation des logements</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Coefficient propre au logement</t>
-  </si>
-  <si>
-    <t>Type de logement</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>Col 1</t>
-  </si>
-  <si>
-    <t>Col 2</t>
-  </si>
-  <si>
-    <t>Col 3</t>
-  </si>
-  <si>
-    <t>Col 4</t>
-  </si>
-  <si>
-    <t>Col 5</t>
-  </si>
-  <si>
-    <t>Col 6</t>
-  </si>
-  <si>
-    <t>Col 7</t>
-  </si>
-  <si>
-    <t>Désignation des logements</t>
+    <t>Financement</t>
+  </si>
+  <si>
+    <t>Surface habitable
+(article R.156-1)</t>
+  </si>
+  <si>
+    <t>Surface des annexes
+Réelle</t>
+  </si>
+  <si>
+    <t>Surface des annexes
+Retenue dans la SU</t>
   </si>
   <si>
     <t>Surface utile
 (surface habitable augmentée de 50% de la surface des annexes)</t>
   </si>
   <si>
-    <t>Surface des annexes
-Retenue dans la SU</t>
-  </si>
-  <si>
-    <t>Surface des annexes
-Réelle</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
-  </si>
-  <si>
-    <t>elle sera calculée automatiquement lors de l'import des logements</t>
-  </si>
-  <si>
     <t>Loyer maximum en € par m² de surface utile</t>
+  </si>
+  <si>
+    <t>Coefficient propre au logement</t>
   </si>
   <si>
     <t>Loyer maximum du logement en €
@@ -135,23 +81,85 @@
     <t>Par défaut, indiquez un coefficient de 1 si vous n’appliquez pas de pondération particulière)</t>
   </si>
   <si>
+    <t>Col 1</t>
+  </si>
+  <si>
+    <t>Col 2</t>
+  </si>
+  <si>
+    <t>Col 3</t>
+  </si>
+  <si>
+    <t>Col 4</t>
+  </si>
+  <si>
+    <t>Col 5</t>
+  </si>
+  <si>
+    <t>Col 6</t>
+  </si>
+  <si>
+    <t>Col 7</t>
+  </si>
+  <si>
+    <t>Col 8</t>
+  </si>
+  <si>
+    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
+  </si>
+  <si>
+    <t>elle sera calculée automatiquement lors de l'import des logements</t>
+  </si>
+  <si>
+    <t>Ici quelques explications</t>
+  </si>
+  <si>
+    <t>1. Telechager le modèle (ce fichier)</t>
+  </si>
+  <si>
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>3. Enregistrer vos modifications</t>
+  </si>
+  <si>
+    <t>4. Téléverser le fichier modifié dans l'application</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+  </si>
+  <si>
+    <t>Type de logement</t>
+  </si>
+  <si>
     <t>lignes data</t>
   </si>
   <si>
-    <t>Surface habitable
-(article R.156-1)</t>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T1bis</t>
+  </si>
+  <si>
+    <t>T1'</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
   </si>
   <si>
     <t>T5</t>
   </si>
   <si>
     <t>T6 et plus</t>
-  </si>
-  <si>
-    <t>T1'</t>
-  </si>
-  <si>
-    <t>T1bis</t>
   </si>
 </sst>
 </file>
@@ -370,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -415,6 +423,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -530,7 +541,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -826,777 +837,827 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08021C90-1ACF-2A4C-A1B0-58A48A8F7007}">
-  <dimension ref="A1:Q52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
+    <col min="2" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
+    <col min="10" max="10" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="H1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="1:17" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="34" t="s">
         <v>15</v>
       </c>
+      <c r="F3" s="34"/>
       <c r="G3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="9"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="24" t="str">
-        <f>IF(F4*G4*H4&gt;0,F4*G4*H4,"")</f>
-        <v/>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" s="14"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="24"/>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="25" t="str">
-        <f>IF(F5*G5*H5&gt;0,F5*G5*H5,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" s="15"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25" t="str">
+        <f t="shared" ref="J5" si="0">IF(G5*H5*I5&gt;0,G5*H5*I5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="24" t="str">
-        <f t="shared" ref="I6:I52" si="0">IF(F6*G6*H6&gt;0,F6*G6*H6,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G6" s="14"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="24" t="str">
+        <f t="shared" ref="J6:J51" si="1">IF(G6*H6*I6&gt;0,G6*H6*I6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="4"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="4"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" s="15"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" s="14"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" s="15"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G12" s="14"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G13" s="15"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G14" s="14"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G15" s="15"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="14"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G17" s="15"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="14"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="15"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G20" s="14"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G21" s="15"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" s="14"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="15"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" s="14"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" s="15"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="14"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="15"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="14"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="15"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="14"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="15"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="14"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="15"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G34" s="14"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" s="15"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G36" s="14"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G37" s="15"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" s="14"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G39" s="15"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="14"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41" s="15"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G42" s="14"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="7"/>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" s="15"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" s="14"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="7"/>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" s="15"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G46" s="14"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="7"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G47" s="15"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G48" s="14"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="7"/>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G49" s="15"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G50" s="14"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="7"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" s="15"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -1606,21 +1667,21 @@
       <c r="G52" s="19"/>
       <c r="H52" s="23"/>
       <c r="I52" s="26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I52" si="2">IF(F52*G52*H52&gt;0,F52*G52*H52,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1643,45 +1704,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467F41B6-50A5-F34D-9811-537B9541F979}">
   <dimension ref="B2:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1693,62 +1754,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4880C39C-0BD9-B447-909B-7F37D33CA805}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E1" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="30">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="31"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/static/files/logements.xlsx
+++ b/static/files/logements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayoub.bouchachia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\production\siap\apilos\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9CB336-2071-427E-BEF6-2274AED39178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55035CC-1F0E-448F-937F-8571E355743A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16110" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Logements" sheetId="1" r:id="rId1"/>
@@ -71,95 +71,95 @@
     <t>Coefficient propre au logement</t>
   </si>
   <si>
+    <t>(Utilisez votre propre nomenclature, elle doit correspondre à celle indiquée dans l’EDD simplifié, ex : 604, Bâtiment B, étage 4, escalier 3, logement N°604)</t>
+  </si>
+  <si>
+    <t>Par défaut, indiquez un coefficient de 1 si vous n’appliquez pas de pondération particulière)</t>
+  </si>
+  <si>
+    <t>Col 1</t>
+  </si>
+  <si>
+    <t>Col 2</t>
+  </si>
+  <si>
+    <t>Col 3</t>
+  </si>
+  <si>
+    <t>Col 4</t>
+  </si>
+  <si>
+    <t>Col 5</t>
+  </si>
+  <si>
+    <t>Col 6</t>
+  </si>
+  <si>
+    <t>Col 7</t>
+  </si>
+  <si>
+    <t>Col 8</t>
+  </si>
+  <si>
+    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
+  </si>
+  <si>
+    <t>elle sera calculée automatiquement lors de l'import des logements</t>
+  </si>
+  <si>
+    <t>Ici quelques explications</t>
+  </si>
+  <si>
+    <t>1. Telechager le modèle (ce fichier)</t>
+  </si>
+  <si>
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>3. Enregistrer vos modifications</t>
+  </si>
+  <si>
+    <t>4. Téléverser le fichier modifié dans l'application</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+  </si>
+  <si>
+    <t>Type de logement</t>
+  </si>
+  <si>
+    <t>lignes data</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T1bis</t>
+  </si>
+  <si>
+    <t>T1'</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>T6 et plus</t>
+  </si>
+  <si>
     <t>Loyer maximum du logement en €
-(col 4 * col 5 * col 6)</t>
-  </si>
-  <si>
-    <t>(Utilisez votre propre nomenclature, elle doit correspondre à celle indiquée dans l’EDD simplifié, ex : 604, Bâtiment B, étage 4, escalier 3, logement N°604)</t>
-  </si>
-  <si>
-    <t>Par défaut, indiquez un coefficient de 1 si vous n’appliquez pas de pondération particulière)</t>
-  </si>
-  <si>
-    <t>Col 1</t>
-  </si>
-  <si>
-    <t>Col 2</t>
-  </si>
-  <si>
-    <t>Col 3</t>
-  </si>
-  <si>
-    <t>Col 4</t>
-  </si>
-  <si>
-    <t>Col 5</t>
-  </si>
-  <si>
-    <t>Col 6</t>
-  </si>
-  <si>
-    <t>Col 7</t>
-  </si>
-  <si>
-    <t>Col 8</t>
-  </si>
-  <si>
-    <t>Attention : ne pas mettre la ligne Total dans ce tableau</t>
-  </si>
-  <si>
-    <t>elle sera calculée automatiquement lors de l'import des logements</t>
-  </si>
-  <si>
-    <t>Ici quelques explications</t>
-  </si>
-  <si>
-    <t>1. Telechager le modèle (ce fichier)</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>3. Enregistrer vos modifications</t>
-  </si>
-  <si>
-    <t>4. Téléverser le fichier modifié dans l'application</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
-  </si>
-  <si>
-    <t>Type de logement</t>
-  </si>
-  <si>
-    <t>lignes data</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T1bis</t>
-  </si>
-  <si>
-    <t>T1'</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>T6 et plus</t>
+(col 5 * col 6 * col 7)</t>
   </si>
 </sst>
 </file>
@@ -875,12 +875,12 @@
         <v>8</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -890,39 +890,39 @@
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
       <c r="I2" s="28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="34" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>15</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,7 +937,7 @@
       <c r="I4" s="21"/>
       <c r="J4" s="24"/>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1712,37 +1712,37 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1761,15 +1761,15 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="29" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="30">
         <v>4</v>
@@ -1777,39 +1777,39 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="31"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="31"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
